--- a/data/hydrogentable_2020.xlsx
+++ b/data/hydrogentable_2020.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6CC4D059-4593-4149-BC41-AA148C3D3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E9D6D91-DD20-174C-A2ED-14693365D093}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6CC4D059-4593-4149-BC41-AA148C3D3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3387BE-CF12-9940-A87B-549D1623AB5C}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="3560" windowWidth="20840" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-540" yWindow="-20500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basicmap" sheetId="8" r:id="rId1"/>
-    <sheet name="inputcoeff_A" sheetId="7" r:id="rId2"/>
+    <sheet name="productioncoeff" sheetId="7" r:id="rId2"/>
     <sheet name="valueaddedcoeff" sheetId="5" r:id="rId3"/>
     <sheet name="jobcoeff" sheetId="4" r:id="rId4"/>
     <sheet name="directemploycoeff" sheetId="6" r:id="rId5"/>
@@ -365,6 +365,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/hydrogentable_2020.xlsx
+++ b/data/hydrogentable_2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6CC4D059-4593-4149-BC41-AA148C3D3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3387BE-CF12-9940-A87B-549D1623AB5C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6CC4D059-4593-4149-BC41-AA148C3D3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B91D5F28-6961-8642-92F2-3A53F6B1D911}"/>
   <bookViews>
-    <workbookView xWindow="-540" yWindow="-20500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basicmap" sheetId="8" r:id="rId1"/>
